--- a/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-12_Fornecedores_Avaliacao.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGI_Sistema-de-gestao-da-qualidade/Registos_SGQ_Plasticom/SGQ-12_Fornecedores_Avaliacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGI_Sistema-de-gestao-da-qualidade\Registos_SGQ_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8713528A-2D34-4627-A353-76369A42457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD57952B-B7DD-41CB-A247-B2512B7EC3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1542,7 +1542,7 @@
     <t>USA</t>
   </si>
   <si>
-    <t>HDPE, LDPE, MDPE</t>
+    <t>HDPE, HDPE-PCR, LDPE, MDPE</t>
   </si>
   <si>
     <t>Produto</t>
